--- a/Employee_Reports_wi48/Mohamed Nasardeen Mohamadu Main Q0436.xlsx
+++ b/Employee_Reports_wi48/Mohamed Nasardeen Mohamadu Main Q0436.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-39</v>
+        <v>-42</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-124</v>
+        <v>-127</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-124</v>
+        <v>-127</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1570,9 +1570,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1584,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1633,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1731,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1768,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1805,11 +1817,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1854,11 +1866,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1903,11 +1915,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1952,11 +1964,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1989,11 +2001,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2441,11 +2453,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -2513,7 +2525,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7939</v>
+        <v>7936</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2542,7 +2554,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7939</v>
+        <v>7936</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2571,7 +2583,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7939</v>
+        <v>7936</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2600,7 +2612,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2629,7 +2641,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2658,7 +2670,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2687,7 +2699,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2716,7 +2728,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7985</v>
+        <v>7982</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2724,6 +2736,383 @@
         </is>
       </c>
       <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>turntable</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>27-May-2048</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>tilting deck</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>05-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>30-May-2048</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>uldtv 20ft</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>05-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>30-May-2048</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>uldtv 15ft</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>05-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>30-May-2048</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>bbtv 20ft</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>05-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>30-May-2048</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>bbtv 15ft</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>05-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>30-May-2048</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>fmc deck</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>27-May-2048</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>27-May-2048</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>non powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>27-May-2048</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>cs placing deck</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>06-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>31-May-2048</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>7990</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>cs input and output conveyor</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>06-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>31-May-2048</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7990</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ball deck</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>27-May-2048</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>7986</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>06-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>31-May-2048</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>7990</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
